--- a/DatosCircuito2026.xlsx
+++ b/DatosCircuito2026.xlsx
@@ -863,14 +863,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 2, 3, 4, 5, 7, 8, 9))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(0, 1, 2, 3, 5, 6, 7, 8, 9)) | (M*=(), A*=(4,))</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L6" t="n">
-        <v>19.9742</v>
+        <v>0.3401</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>1.020728945732117</v>
       </c>
       <c r="U6" t="n">
-        <v>25.683</v>
+        <v>0.594</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>1.020728945732117</v>
       </c>
       <c r="AD6" t="n">
-        <v>27.3833</v>
+        <v>0.9387</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>1.020728945732117</v>
       </c>
       <c r="AM6" t="n">
-        <v>25.3582</v>
+        <v>1.4343</v>
       </c>
     </row>
     <row r="7">
@@ -1007,14 +1007,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 2, 3, 4, 5, 6, 7, 8)) | (M*=(), A*=(9,))</t>
+          <t>(M=(), A=(8,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 2, 3, 4, 5, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2360677123069763</v>
+        <v>0.03219357132911682</v>
       </c>
       <c r="L7" t="n">
-        <v>16.9737</v>
+        <v>0.2891</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="U7" t="n">
-        <v>24.905</v>
+        <v>0.5505</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="AD7" t="n">
-        <v>28.2306</v>
+        <v>1.4676</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="AM7" t="n">
-        <v>25.9723</v>
+        <v>1.7322</v>
       </c>
     </row>
     <row r="8">
@@ -1151,14 +1151,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 2, 3, 4, 5, 6, 7, 8, 9)) | (M*=(), A*=(0,))</t>
+          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(0, 1, 2, 3, 4, 5, 6, 7, 9)) | (M*=(), A*=(8,))</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.07894390821456909</v>
+        <v>0.01744508743286133</v>
       </c>
       <c r="L8" t="n">
-        <v>20.2631</v>
+        <v>0.2577</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="U8" t="n">
-        <v>27.4484</v>
+        <v>3.3557</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="AD8" t="n">
-        <v>27.5345</v>
+        <v>3.8425</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="AM8" t="n">
-        <v>21.9493</v>
+        <v>3.4888</v>
       </c>
     </row>
     <row r="9">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>(M=(), A=(0,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 2, 3, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.02332454919815063</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L9" t="n">
-        <v>15.3515</v>
+        <v>0.2568</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="U9" t="n">
-        <v>23.032</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="AD9" t="n">
-        <v>22.5592</v>
+        <v>1.4429</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="AM9" t="n">
-        <v>23.0861</v>
+        <v>1.9901</v>
       </c>
     </row>
     <row r="10">
@@ -1439,14 +1439,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(0, 1, 2, 3, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.0629742443561554</v>
+        <v>0.001722872257232666</v>
       </c>
       <c r="L10" t="n">
-        <v>11.9741</v>
+        <v>0.339</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="U10" t="n">
-        <v>6.2251</v>
+        <v>0.488</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.8784</v>
+        <v>0.8337</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.0206</v>
+        <v>1.8598</v>
       </c>
     </row>
     <row r="11">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(M=(), A=(7,)) | (M*=(0, 2, 4, 6, 8), A*=(0, 1, 2, 3, 4, 5, 6, 8, 9))</t>
+          <t>(M=(0, 2, 4, 6, 8), A=(0, 1, 2, 3, 4, 5, 6, 8, 9)) | (M*=(), A*=(7,))</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>0.0002434253692626953</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3815</v>
+        <v>0.2695</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1616,14 +1616,14 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 2, 3, 4, 5, 6, 7, 8, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 1, 2, 3, 4, 5, 6, 8, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0151</v>
+        <v>0.6626</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 2, 3, 4, 5, 6, 7, 8, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 1, 2, 3, 4, 5, 6, 8, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3408</v>
+        <v>0.6766</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.3003</v>
+        <v>0.8073</v>
       </c>
     </row>
     <row r="12">
@@ -1727,14 +1727,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>(M=(), A=(8,)) | (M*=(1, 3, 5, 7, 9), A*=(0, 1, 2, 3, 4, 5, 6, 7, 9))</t>
+          <t>(M=(), A=(3,)) | (M*=(1, 3, 5, 7, 9), A*=(0, 1, 2, 4, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.0008718371391296387</v>
+        <v>5.492568016052246e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8184</v>
+        <v>0.279</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6198</v>
+        <v>0.3058</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6888</v>
+        <v>1.1737</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3053</v>
+        <v>1.1532</v>
       </c>
     </row>
     <row r="13">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 2, 3, 4, 5, 7, 8))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(0, 1, 2, 3, 5, 6, 7, 8)) | (M*=(), A*=(4,))</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L13" t="n">
-        <v>19.1396</v>
+        <v>0.5703</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>0.9033668041229248</v>
       </c>
       <c r="U13" t="n">
-        <v>9.5961</v>
+        <v>0.9107</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>0.9033668041229248</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.197900000000001</v>
+        <v>1.1556</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0.9033668041229248</v>
       </c>
       <c r="AM13" t="n">
-        <v>6.4497</v>
+        <v>1.4472</v>
       </c>
     </row>
     <row r="14">
@@ -2015,14 +2015,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>(M=(), A=(3,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 2, 4, 5, 6, 7, 8))</t>
+          <t>(M=(), A=(8,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 2, 3, 4, 5, 6, 7))</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.1534166634082794</v>
+        <v>0.03219357132911682</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0651</v>
+        <v>0.339</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8), A=(0, 1, 2, 3, 5, 6, 7, 8)) | G1(M=(4,), A=(4,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 5, 6, 7, 8)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>0.8964061141014099</v>
+        <v>0.7580173015594482</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8163</v>
+        <v>0.6411</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>0.7580173015594482</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.9429</v>
+        <v>0.782</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>0.7580173015594482</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.2436</v>
+        <v>1.5565</v>
       </c>
     </row>
     <row r="15">
@@ -2159,14 +2159,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>(M=(), A=(0,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 2, 3, 4, 5, 6, 7, 8))</t>
+          <t>(M=(), A=(8,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 2, 3, 4, 5, 6, 7))</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.07894390821456909</v>
+        <v>0.01744508743286133</v>
       </c>
       <c r="L15" t="n">
-        <v>20.9526</v>
+        <v>0.3543</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="U15" t="n">
-        <v>8.886900000000001</v>
+        <v>1.7277</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.7665</v>
+        <v>2.792</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.4839</v>
+        <v>2.6356</v>
       </c>
     </row>
     <row r="16">
@@ -2303,14 +2303,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8)) | (M*=(), A*=(0,))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 2, 3, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.02332454919815063</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L16" t="n">
-        <v>3.04</v>
+        <v>0.3379</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5023</v>
+        <v>1.2702</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.819</v>
+        <v>1.6601</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.2525</v>
+        <v>1.2349</v>
       </c>
     </row>
     <row r="17">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(0, 1, 2, 3, 4, 6, 7, 8))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(0, 1, 2, 3, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.0629742443561554</v>
+        <v>0.001722872257232666</v>
       </c>
       <c r="L17" t="n">
-        <v>12.3334</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="U17" t="n">
-        <v>7.7577</v>
+        <v>0.802</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.8885</v>
+        <v>0.7733</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.1464</v>
+        <v>1.6633</v>
       </c>
     </row>
     <row r="18">
@@ -2591,14 +2591,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>(M=(0, 2, 4, 6, 8), A=(0, 1, 2, 3, 4, 5, 6, 8)) | (M*=(), A*=(7,))</t>
+          <t>(M=(), A=(7,)) | (M*=(0, 2, 4, 6, 8), A*=(0, 1, 2, 3, 4, 5, 6, 8))</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>0.0002434253692626953</v>
       </c>
       <c r="L18" t="n">
-        <v>0.385</v>
+        <v>0.5419</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4225</v>
+        <v>0.2609</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1888</v>
+        <v>0.3234</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.361</v>
+        <v>0.6701</v>
       </c>
     </row>
     <row r="19">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>(M=(), A=(8,)) | (M*=(1, 3, 5, 7, 9), A*=(0, 1, 2, 3, 4, 5, 6, 7))</t>
+          <t>(M=(), A=(3,)) | (M*=(1, 3, 5, 7, 9), A*=(0, 1, 2, 4, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.0008718371391296387</v>
+        <v>5.492568016052246e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3258</v>
+        <v>0.108</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5041</v>
+        <v>0.2075</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.7111</v>
+        <v>0.5342</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.6567</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="20">
@@ -2879,14 +2879,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 2, 3, 4, 5, 7, 8, 9))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 2, 3, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L20" t="n">
-        <v>10.5831</v>
+        <v>0.2231</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>1.005450248718262</v>
       </c>
       <c r="U20" t="n">
-        <v>10.2435</v>
+        <v>0.4909</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>1.005450248718262</v>
       </c>
       <c r="AD20" t="n">
-        <v>10.235</v>
+        <v>0.8401</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>1.005450248718262</v>
       </c>
       <c r="AM20" t="n">
-        <v>10.867</v>
+        <v>1.3604</v>
       </c>
     </row>
     <row r="21">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8)) | (M*=(), A*=(9,))</t>
+          <t>(M=(), A=(8,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 4, 5, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.2360677123069763</v>
+        <v>0.03219357132911682</v>
       </c>
       <c r="L21" t="n">
-        <v>10.9248</v>
+        <v>0.4153</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="U21" t="n">
-        <v>9.4655</v>
+        <v>0.3573</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="AD21" t="n">
-        <v>10.9049</v>
+        <v>0.9426</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>G0(M=(0,), A=()) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8, 9))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="AL21" t="n">
-        <v>0.8344689011573792</v>
+        <v>0.2360677123069763</v>
       </c>
       <c r="AM21" t="n">
-        <v>10.3357</v>
+        <v>1.532</v>
       </c>
     </row>
     <row r="22">
@@ -3167,14 +3167,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 2, 3, 4, 5, 6, 7, 9)) | (M*=(), A*=(8,))</t>
+          <t>(M=(), A=(8,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 2, 3, 4, 5, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>0.01744508743286133</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1697</v>
+        <v>0.5103</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>0.6676848530769348</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1189</v>
+        <v>0.3372</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>0.6676848530769348</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4376</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>0.6676848530769348</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4632</v>
+        <v>0.8094</v>
       </c>
     </row>
     <row r="23">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>(M=(), A=(9,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 4, 5, 6, 7, 8))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.2242002487182617</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1672</v>
+        <v>0.2255</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0.2242002487182617</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3606</v>
+        <v>0.2783</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>0.2242002487182617</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5279</v>
+        <v>0.4601</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>0.2242002487182617</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.9463</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="24">
@@ -3455,14 +3455,14 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 2, 3, 4, 6, 7, 8, 9))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 2, 3, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.0629742443561554</v>
+        <v>0.001722872257232666</v>
       </c>
       <c r="L24" t="n">
-        <v>6.4909</v>
+        <v>0.221</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 2, 3, 4, 5, 6, 7, 9)) | G1(M=(), A=(8,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 2, 3, 4, 6, 7, 8, 9)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0.08928036689758301</v>
+        <v>0.0629742443561554</v>
       </c>
       <c r="U24" t="n">
-        <v>4.9562</v>
+        <v>0.4303</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.8807</v>
+        <v>0.7801</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AM24" t="n">
-        <v>3.9292</v>
+        <v>1.0264</v>
       </c>
     </row>
     <row r="25">
@@ -3606,7 +3606,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9655</v>
+        <v>0.229</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3632,14 +3632,14 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(2, 3, 4, 5, 6, 7, 8, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(1, 2, 3, 4, 5, 6, 8, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9322</v>
+        <v>0.3044</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(2, 3, 4, 5, 6, 7, 8, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(1, 2, 3, 4, 5, 6, 8, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.6558</v>
+        <v>0.515</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5212</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="26">
@@ -3743,14 +3743,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>(M=(1, 3, 5, 7, 9), A=(1, 2, 3, 4, 5, 6, 7, 9)) | (M*=(), A*=(8,))</t>
+          <t>(M=(), A=(3,)) | (M*=(1, 3, 5, 7, 9), A*=(1, 2, 4, 5, 6, 7, 8, 9))</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.0008718371391296387</v>
+        <v>5.492568016052246e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3946</v>
+        <v>0.4815</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="U26" t="n">
-        <v>0.647</v>
+        <v>0.6921</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.2802</v>
+        <v>0.742</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.4146</v>
+        <v>0.7058</v>
       </c>
     </row>
     <row r="27">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 2, 3, 4, 5, 7, 8)) | (M*=(), A*=(6,))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 2, 3, 5, 6, 7, 8)) | (M*=(), A*=(4,))</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L27" t="n">
-        <v>11.3009</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3920,14 +3920,14 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 9), A=(1,)) | G1(M=(2, 3, 4, 5, 6, 7, 8), A=(2, 3, 4, 5, 6, 7, 8))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 7, 8, 9), A=(1, 2, 3, 4, 5, 7, 8)) | G1(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>1.581951141357422</v>
+        <v>0.8880881071090698</v>
       </c>
       <c r="U27" t="n">
-        <v>7.2641</v>
+        <v>0.7867</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>0.8880881071090698</v>
       </c>
       <c r="AD27" t="n">
-        <v>8.4208</v>
+        <v>0.833</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>0.8880881071090698</v>
       </c>
       <c r="AM27" t="n">
-        <v>7.9423</v>
+        <v>1.0235</v>
       </c>
     </row>
     <row r="28">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 4, 5, 6, 7, 8)) | (M*=(), A*=(3,))</t>
+          <t>(M=(), A=(8,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 4, 5, 6, 7))</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.1534166634082794</v>
+        <v>0.03219357132911682</v>
       </c>
       <c r="L28" t="n">
-        <v>2.7046</v>
+        <v>0.5765</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -4064,14 +4064,14 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>G0(M=(0,), A=()) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8), A=(1, 3, 4, 5, 6, 7, 8)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>0.8226014375686646</v>
+        <v>0.6965432167053223</v>
       </c>
       <c r="U28" t="n">
-        <v>1.146</v>
+        <v>0.361</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>G0(M=(0,), A=()) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8), A=(1, 3, 4, 5, 6, 7, 8)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>0.8226014375686646</v>
+        <v>0.6965432167053223</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2453</v>
+        <v>0.4835</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4130,14 +4130,14 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>G0(M=(0,), A=()) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 2, 3, 4, 5, 6, 7, 8))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8), A=(1, 3, 4, 5, 6, 7, 8)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AL28" t="n">
-        <v>0.8226014375686646</v>
+        <v>0.6965432167053223</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.5312</v>
+        <v>0.9572000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -4182,7 +4182,7 @@
         <v>0.01744508743286133</v>
       </c>
       <c r="L29" t="n">
-        <v>2.3366</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>0.4577630758285522</v>
       </c>
       <c r="U29" t="n">
-        <v>1.372</v>
+        <v>0.7845</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>0.4577630758285522</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.358</v>
+        <v>0.7351</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>0.4577630758285522</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.9319</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="30">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(2, 3, 4, 5, 6, 7, 8)) | (M*=(), A*=(1,))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(1, 2, 3, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.03661090135574341</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3833</v>
+        <v>0.1127</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>0.2774369120597839</v>
       </c>
       <c r="U30" t="n">
-        <v>0.3777</v>
+        <v>0.1878</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>0.2774369120597839</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.1235</v>
+        <v>0.3743</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>0.2774369120597839</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.2162</v>
+        <v>0.5409</v>
       </c>
     </row>
     <row r="31">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 2, 3, 4, 6, 7, 8))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 2, 3, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.0629742443561554</v>
+        <v>0.001722872257232666</v>
       </c>
       <c r="L31" t="n">
-        <v>3.4375</v>
+        <v>0.1294</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 2, 3, 4, 5, 6, 7)) | G1(M=(), A=(8,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 2, 3, 4, 6, 7, 8)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>0.08928036689758301</v>
+        <v>0.0629742443561554</v>
       </c>
       <c r="U31" t="n">
-        <v>2.54</v>
+        <v>0.4179</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.5156</v>
+        <v>0.646</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AM31" t="n">
-        <v>2.364</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="32">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>(M=(), A=(8,)) | (M*=(1, 3, 5, 7, 9), A*=(1, 2, 3, 4, 5, 6, 7))</t>
+          <t>(M=(), A=(3,)) | (M*=(1, 3, 5, 7, 9), A*=(1, 2, 4, 5, 6, 7, 8))</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.0008718371391296387</v>
+        <v>5.492568016052246e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4046</v>
+        <v>0.131</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="U33" t="n">
-        <v>0.1335</v>
+        <v>0.2565</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.1121</v>
+        <v>0.4288</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>0.0008718371391296387</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.2371</v>
+        <v>0.4945</v>
       </c>
     </row>
     <row r="34">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 3, 4, 7, 9))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 3, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L34" t="n">
-        <v>8.9795</v>
+        <v>0.2067</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4928,14 +4928,14 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 9), A=(0, 1, 3, 4, 6, 7, 9)) | G1(M=(5,), A=()) | G2(M=(8,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 7, 8, 9), A=(0, 1, 3, 4, 7, 9)) | G1(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>0.9613670706748962</v>
+        <v>0.8278033137321472</v>
       </c>
       <c r="U34" t="n">
-        <v>8.549300000000001</v>
+        <v>0.4905</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -4961,14 +4961,14 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 9), A=(0, 1, 3, 4, 6, 7, 9)) | G1(M=(5,), A=()) | G2(M=(8,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 7, 8, 9), A=(0, 1, 3, 4, 7, 9)) | G1(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>0.9613670706748962</v>
+        <v>0.8278033137321472</v>
       </c>
       <c r="AD34" t="n">
-        <v>7.6389</v>
+        <v>0.6995</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 9), A=(0, 1, 3, 4, 6, 7, 9)) | G1(M=(5,), A=()) | G2(M=(8,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 7, 8, 9), A=(0, 1, 3, 4, 7, 9)) | G1(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="AL34" t="n">
-        <v>0.9613670706748962</v>
+        <v>0.8278033137321472</v>
       </c>
       <c r="AM34" t="n">
-        <v>6.3836</v>
+        <v>0.9147999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 6, 7)) | (M*=(), A*=(9,))</t>
+          <t>(M=(), A=(1,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.2360677123069763</v>
+        <v>0.05244863033294678</v>
       </c>
       <c r="L35" t="n">
-        <v>8.231400000000001</v>
+        <v>0.2213</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 8), A=(0, 1, 3, 4, 6, 7, 9)) | G1(M=(5,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 6, 7)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>0.7485858798027039</v>
+        <v>0.2360677123069763</v>
       </c>
       <c r="U35" t="n">
-        <v>8.159000000000001</v>
+        <v>0.3193</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -5105,14 +5105,14 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 8), A=(0, 1, 3, 4, 6, 7, 9)) | G1(M=(5,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 6, 7)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>0.7485858798027039</v>
+        <v>0.2360677123069763</v>
       </c>
       <c r="AD35" t="n">
-        <v>7.7727</v>
+        <v>0.4722</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>0.2360677123069763</v>
       </c>
       <c r="AM35" t="n">
-        <v>4.841</v>
+        <v>0.7423999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>(M=(), A=(0,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 3, 4, 6, 7, 9))</t>
+          <t>(M=(), A=(9,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(0, 1, 3, 4, 6, 7))</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.07894390821456909</v>
+        <v>0.03987503051757812</v>
       </c>
       <c r="L36" t="n">
-        <v>6.3147</v>
+        <v>0.131</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="U36" t="n">
-        <v>7.2483</v>
+        <v>0.2786</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5249,14 +5249,14 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>G0(M=(8,), A=(0,)) | G1(M=(1, 3, 4, 5, 6, 7, 9), A=(1, 3, 4, 6, 7, 9)) | G2(M=(2,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>0.6566015481948853</v>
+        <v>0.07894390821456909</v>
       </c>
       <c r="AD36" t="n">
-        <v>7.5542</v>
+        <v>0.5202</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>G0(M=(8,), A=(0,)) | G1(M=(1, 3, 4, 5, 6, 7, 9), A=(1, 3, 4, 6, 7, 9)) | G2(M=(2,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(1, 3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="AL36" t="n">
-        <v>0.6566015481948853</v>
+        <v>0.07894390821456909</v>
       </c>
       <c r="AM36" t="n">
-        <v>7.1154</v>
+        <v>0.6704</v>
       </c>
     </row>
     <row r="37">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 6, 7)) | (M*=(), A*=(9,))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 1, 3, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.2242002487182617</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L37" t="n">
-        <v>7.4943</v>
+        <v>0.1479</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="U37" t="n">
-        <v>6.4149</v>
+        <v>0.3389</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(0, 1, 3, 4, 6, 7)) | G1(M=(), A=(9,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>0.2242002487182617</v>
+        <v>0.02332454919815063</v>
       </c>
       <c r="AD37" t="n">
-        <v>6.5777</v>
+        <v>0.6573</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>0.02332454919815063</v>
       </c>
       <c r="AM37" t="n">
-        <v>6.5831</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="38">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>(M=(), A=(0,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 3, 4, 6, 7, 9))</t>
+          <t>(M=(0, 1, 3, 4, 6, 7, 9), A=(0, 1, 3, 6, 7, 9)) | (M*=(), A*=(4,))</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.02950543165206909</v>
+        <v>0.001722872257232666</v>
       </c>
       <c r="L38" t="n">
-        <v>0.164</v>
+        <v>0.1448</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>0.2764834761619568</v>
       </c>
       <c r="U38" t="n">
-        <v>0.2763</v>
+        <v>0.1629</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>G0(M=(0, 3, 6, 7, 9), A=(0, 3, 6, 7, 9)) | G1(M=(1,), A=(1,)) | G2(M=(4,), A=(4,))</t>
+          <t>G0(M=(0,), A=(0,)) | G1(M=(1,), A=(1,)) | G2(M=(3, 4, 6, 7, 9), A=(3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>0.2823602259159088</v>
+        <v>0.2764834761619568</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.1082</v>
+        <v>0.2615</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5570,14 +5570,14 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>G0(M=(0, 3, 6, 7, 9), A=(0, 3, 6, 7, 9)) | G1(M=(1,), A=(1,)) | G2(M=(4,), A=(4,))</t>
+          <t>G0(M=(0,), A=(0,)) | G1(M=(1,), A=(1,)) | G2(M=(3, 4, 6, 7, 9), A=(3, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="AL38" t="n">
-        <v>0.2823602259159088</v>
+        <v>0.2764834761619568</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.1114</v>
+        <v>0.4634</v>
       </c>
     </row>
     <row r="39">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>(M=(), A=(7,)) | (M*=(0, 2, 4, 6, 8), A*=(0, 1, 3, 4, 6, 9))</t>
+          <t>(M=(0, 2, 4, 6, 8), A=(0, 1, 3, 4, 6, 9)) | (M*=(), A*=(7,))</t>
         </is>
       </c>
       <c r="K39" t="n">
         <v>0.0002434253692626953</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2187</v>
+        <v>0.1496</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -5648,14 +5648,14 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 3, 4, 6, 7, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(0, 1, 3, 4, 6, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1453</v>
+        <v>0.1815</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.1364</v>
+        <v>0.2662</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.12</v>
+        <v>0.5351</v>
       </c>
     </row>
     <row r="40">
@@ -5759,14 +5759,14 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>(M=(1, 3, 5, 7, 9), A=(0, 1, 3, 4, 7, 9)) | (M*=(), A*=(6,))</t>
+          <t>(M=(), A=(3,)) | (M*=(1, 3, 5, 7, 9), A*=(0, 1, 4, 6, 7, 9))</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.04233419895172119</v>
+        <v>5.492568016052246e-05</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1762</v>
+        <v>0.1719</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>0.04233419895172119</v>
       </c>
       <c r="U40" t="n">
-        <v>0.0542</v>
+        <v>0.2448</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>0.04233419895172119</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.0979</v>
+        <v>0.2674</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>0.04233419895172119</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.0925</v>
+        <v>0.5283</v>
       </c>
     </row>
     <row r="41">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(0, 2, 4, 8)) | (M*=(), A*=(6,))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A=(0, 2, 6, 8)) | (M*=(), A*=(4,))</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.05388635396957397</v>
+        <v>0.0468297004699707</v>
       </c>
       <c r="L41" t="n">
-        <v>0.719</v>
+        <v>0.2488</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -5936,14 +5936,14 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 5, 6, 8), A=(0, 2, 6, 8)) | G1(M=(4, 7, 9), A=(4,))</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 7, 8, 9), A=(0, 2, 8)) | G1(M=(4,), A=(4,)) | G2(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="T41" t="n">
-        <v>0.3968162536621094</v>
+        <v>0.3078100383281708</v>
       </c>
       <c r="U41" t="n">
-        <v>0.506</v>
+        <v>0.6682</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -5969,14 +5969,14 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 5, 6, 8, 9), A=(0, 6, 8)) | G1(M=(2, 3, 4, 7), A=(2, 4))</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 7, 8, 9), A=(0, 2, 8)) | G1(M=(4,), A=(4,)) | G2(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>0.3453046679496765</v>
+        <v>0.3078100383281708</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.6025</v>
+        <v>1.2254</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -6002,14 +6002,14 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 5, 6, 8, 9), A=(0, 6, 8)) | G1(M=(2, 3, 4, 7), A=(2, 4))</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 7, 8, 9), A=(0, 2, 8)) | G1(M=(4,), A=(4,)) | G2(M=(6,), A=(6,))</t>
         </is>
       </c>
       <c r="AL41" t="n">
-        <v>0.3453046679496765</v>
+        <v>0.3078100383281708</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.6263</v>
+        <v>1.0974</v>
       </c>
     </row>
     <row r="42">
@@ -6047,14 +6047,14 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>(M=(2, 7), A=(2, 8)) | (M*=(0, 1, 3, 4, 5, 6, 8), A*=(0, 4, 6))</t>
+          <t>(M=(), A=(8,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 2, 4, 6))</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.226404070854187</v>
+        <v>0.03219357132911682</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5349</v>
+        <v>0.4795</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -6080,14 +6080,14 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 4, 6, 8), A=(0, 2, 4, 6, 8)) | G1(M=(3,), A=()) | G2(M=(5, 7), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 8), A=(0, 4, 6, 8)) | G1(M=(2, 7), A=(2,))</t>
         </is>
       </c>
       <c r="T42" t="n">
-        <v>0.3213750123977661</v>
+        <v>0.2468926608562469</v>
       </c>
       <c r="U42" t="n">
-        <v>0.1752</v>
+        <v>0.2939</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 4, 6, 8), A=(0, 2, 4, 6, 8)) | G1(M=(3,), A=()) | G2(M=(5,), A=()) | G3(M=(7,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 8), A=(0, 4, 6, 8)) | G1(M=(2, 7), A=(2,))</t>
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>0.3213750123977661</v>
+        <v>0.2468926608562469</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.1599</v>
+        <v>0.326</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -6146,14 +6146,14 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 4, 6, 8), A=(0, 2, 4, 6, 8)) | G1(M=(3,), A=()) | G2(M=(5,), A=()) | G3(M=(7,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 8), A=(0, 4, 6, 8)) | G1(M=(2, 7), A=(2,))</t>
         </is>
       </c>
       <c r="AL42" t="n">
-        <v>0.3213750123977661</v>
+        <v>0.2468926608562469</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.1659</v>
+        <v>0.3631</v>
       </c>
     </row>
     <row r="43">
@@ -6198,7 +6198,7 @@
         <v>0.01744508743286133</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5809</v>
+        <v>0.2732</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="U43" t="n">
-        <v>0.5327</v>
+        <v>0.3939</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6257,14 +6257,14 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 4, 5, 6, 7, 9), A=(0, 2, 4, 6)) | G1(M=(3, 8), A=(8,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9), A=(2, 4, 6, 8))</t>
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>0.2839646935462952</v>
+        <v>0.07894390821456909</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.3336</v>
+        <v>0.9012</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>0.07894390821456909</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.4974</v>
+        <v>0.5845</v>
       </c>
     </row>
     <row r="44">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 7, 8), A=(2, 8)) | (M*=(4, 5, 6), A*=(0, 4, 6))</t>
+          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8), A*=(0, 2, 6, 8))</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.05011677742004395</v>
+        <v>0.0009173750877380371</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4674</v>
+        <v>0.1222</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -6368,14 +6368,14 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>G0(M=(4, 5, 6), A=(0, 4, 6)) | G1(M=(1, 2, 3, 7, 8), A=(2, 8))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(2, 4, 6, 8))</t>
         </is>
       </c>
       <c r="T44" t="n">
-        <v>0.05011677742004395</v>
+        <v>0.02332454919815063</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1571</v>
+        <v>0.255</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>0.0605197548866272</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.2113</v>
+        <v>0.3862</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>0.0605197548866272</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.1825</v>
+        <v>0.3786</v>
       </c>
     </row>
     <row r="45">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9), A=(0, 2, 6, 8)) | (M*=(), A*=(4,))</t>
+          <t>(M=(), A=(4,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(0, 2, 6, 8))</t>
         </is>
       </c>
       <c r="K45" t="n">
         <v>0.001722872257232666</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3181</v>
+        <v>0.4458</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -6512,14 +6512,14 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 4, 6, 7), A=(0, 2, 4, 6, 8)) | G1(M=(3, 9), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(0, 2, 4, 6)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T45" t="n">
-        <v>0.1134249269962311</v>
+        <v>0.08928036689758301</v>
       </c>
       <c r="U45" t="n">
-        <v>0.1114</v>
+        <v>0.3119</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6545,14 +6545,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 4, 6, 7), A=(0, 2, 4, 6, 8)) | G1(M=(3,), A=()) | G2(M=(9,), A=())</t>
+          <t>G0(M=(0, 3, 9), A=(0, 2)) | G1(M=(1, 4, 6, 7), A=(4, 6, 8))</t>
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>0.1134249269962311</v>
+        <v>0.1042019724845886</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.0882</v>
+        <v>0.2866</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6578,14 +6578,14 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 4, 6, 7), A=(0, 2, 4, 6, 8)) | G1(M=(3,), A=()) | G2(M=(9,), A=())</t>
+          <t>G0(M=(0, 3, 9), A=(0, 2)) | G1(M=(1, 4, 6, 7), A=(4, 6, 8))</t>
         </is>
       </c>
       <c r="AL45" t="n">
-        <v>0.1134249269962311</v>
+        <v>0.1042019724845886</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.1638</v>
+        <v>0.5053</v>
       </c>
     </row>
     <row r="46">
@@ -6911,14 +6911,14 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 7, 8, 9), A=(1, 3, 5, 7, 9)) | (M*=(6,), A*=())</t>
+          <t>(M=(), A=(9,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9), A*=(1, 3, 5, 7))</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.6034383773803711</v>
+        <v>0.1305142641067505</v>
       </c>
       <c r="L48" t="n">
-        <v>1.0843</v>
+        <v>0.165</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>0.6034383773803711</v>
       </c>
       <c r="U48" t="n">
-        <v>0.5405</v>
+        <v>0.2705</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>0.6034383773803711</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.6276</v>
+        <v>0.4169</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>0.6034383773803711</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.5192</v>
+        <v>0.4528</v>
       </c>
     </row>
     <row r="49">
@@ -7206,7 +7206,7 @@
         <v>0.03987503051757812</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4318</v>
+        <v>0.4726</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -7232,14 +7232,14 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7), A=(1, 3, 5, 7)) | G1(M=(6, 8, 9), A=(9,))</t>
+          <t>G0(M=(1, 3, 4, 5, 6, 7, 9), A=(1, 3, 5, 7, 9)) | G1(M=(2, 8), A=())</t>
         </is>
       </c>
       <c r="T50" t="n">
-        <v>0.3506795167922974</v>
+        <v>0.269940048456192</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2649</v>
+        <v>0.4139</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7265,14 +7265,14 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7), A=(1, 3, 5, 7)) | G1(M=(6, 8, 9), A=(9,))</t>
+          <t>G0(M=(1, 3, 4, 5, 6, 7, 9), A=(1, 3, 5, 7, 9)) | G1(M=(2, 8), A=())</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>0.3506795167922974</v>
+        <v>0.269940048456192</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.1925</v>
+        <v>0.4488</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>0.269940048456192</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.1688</v>
+        <v>0.4648</v>
       </c>
     </row>
     <row r="51">
@@ -7350,7 +7350,7 @@
         <v>0.03661090135574341</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5131</v>
+        <v>0.3902</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -7376,14 +7376,14 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7), A=(1, 3, 5, 7, 9)) | G1(M=(8,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 3, 5, 7)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="T51" t="n">
-        <v>0.3371366262435913</v>
+        <v>0.2242002487182617</v>
       </c>
       <c r="U51" t="n">
-        <v>0.3088</v>
+        <v>0.1581</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7409,14 +7409,14 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7), A=(1, 3, 5, 7, 9)) | G1(M=(8,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 3, 5, 7)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>0.3371366262435913</v>
+        <v>0.2242002487182617</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.1999</v>
+        <v>0.3323</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7), A=(1, 3, 5, 7, 9)) | G1(M=(8,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8), A=(1, 3, 5, 7)) | G1(M=(), A=(9,))</t>
         </is>
       </c>
       <c r="AL51" t="n">
-        <v>0.3371366262435913</v>
+        <v>0.2242002487182617</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.16</v>
+        <v>0.5483</v>
       </c>
     </row>
     <row r="52">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 3, 4, 6, 7, 9), A*=(1, 3, 7, 9))</t>
+          <t>(M=(0, 1, 3, 4, 6, 7, 9), A=(3, 5, 7, 9)) | (M*=(), A*=(1,))</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.0629742443561554</v>
+        <v>0.001923650503158569</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2842</v>
+        <v>0.3966</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -7520,14 +7520,14 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>G0(M=(0, 3, 4, 6, 7, 9), A=(3, 5, 7, 9)) | G1(M=(1,), A=(1,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 3, 7, 9)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T52" t="n">
-        <v>0.1534030437469482</v>
+        <v>0.0629742443561554</v>
       </c>
       <c r="U52" t="n">
-        <v>0.0944</v>
+        <v>0.2046</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7553,14 +7553,14 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>G0(M=(0, 3, 4, 6, 7, 9), A=(3, 5, 7, 9)) | G1(M=(1,), A=(1,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9), A=(1, 3, 7, 9)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>0.1534030437469482</v>
+        <v>0.0629742443561554</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.1013</v>
+        <v>0.3682</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>0.0629742443561554</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="53">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>(M=(0, 2, 4, 6, 8), A=(3, 5, 7, 9)) | (M*=(), A*=(1,))</t>
+          <t>(M=(), A=(7,)) | (M*=(0, 2, 4, 6, 8), A*=(1, 3, 5, 9))</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="L53" t="n">
-        <v>0.229</v>
+        <v>0.3863</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -7664,14 +7664,14 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(3, 5, 7, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(1, 3, 5, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="T53" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="U53" t="n">
-        <v>0.1267</v>
+        <v>0.2847</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7697,14 +7697,14 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8), A=(3, 5, 7, 9)) | G1(M=(), A=(1,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8), A=(1, 3, 5, 9)) | G1(M=(), A=(7,))</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>0.05109912157058716</v>
+        <v>0.0002434253692626953</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.1656</v>
+        <v>0.3995</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>0.0002434253692626953</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.1328</v>
+        <v>0.5107</v>
       </c>
     </row>
     <row r="54">
@@ -7782,7 +7782,7 @@
         <v>5.492568016052246e-05</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0251</v>
+        <v>0.0559</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -7808,14 +7808,14 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7), A=(1, 3, 5, 7)) | G1(M=(9,), A=(9,))</t>
+          <t>G0(M=(1, 5, 7, 9), A=(1, 5, 7, 9)) | G1(M=(3,), A=(3,))</t>
         </is>
       </c>
       <c r="T54" t="n">
-        <v>0.1328566372394562</v>
+        <v>0.09544956684112549</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0325</v>
+        <v>0.0391</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7841,14 +7841,14 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7), A=(1, 3, 5, 7)) | G1(M=(9,), A=(9,))</t>
+          <t>G0(M=(1, 5, 7, 9), A=(1, 5, 7, 9)) | G1(M=(3,), A=(3,))</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0.1328566372394562</v>
+        <v>0.09544956684112549</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.0184</v>
+        <v>0.0514</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>0.09544956684112549</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0165</v>
+        <v>0.0366</v>
       </c>
     </row>
   </sheetData>
@@ -7891,12 +7891,12 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="M3:U3"/>
     <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="V3:AD3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="AB4:AD4"/>
     <mergeCell ref="P4:R4"/>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14)) | (M*=(), A*=(6,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.4428481459617615</v>
+        <v>0.01416301727294922</v>
       </c>
       <c r="L6" t="n">
-        <v>22.6935</v>
+        <v>5.4467</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8340,14 +8340,14 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>2.592115879058838</v>
+        <v>1.994701862335205</v>
       </c>
       <c r="U6" t="n">
-        <v>19.0211</v>
+        <v>13.9383</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>2.592115879058838</v>
+        <v>1.994701862335205</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.8348</v>
+        <v>13.1144</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -8406,14 +8406,14 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(8,), A=(8,))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL6" t="n">
-        <v>2.341389656066895</v>
+        <v>1.994701862335205</v>
       </c>
       <c r="AM6" t="n">
-        <v>15.579</v>
+        <v>18.3483</v>
       </c>
     </row>
     <row r="7">
@@ -8451,14 +8451,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(14,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.07223978638648987</v>
+        <v>0.05528867244720459</v>
       </c>
       <c r="L7" t="n">
-        <v>10.4349</v>
+        <v>2.5659</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="U7" t="n">
-        <v>10.2722</v>
+        <v>4.7943</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AD7" t="n">
-        <v>10.2728</v>
+        <v>10.3071</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AM7" t="n">
-        <v>10.2765</v>
+        <v>11.6145</v>
       </c>
     </row>
     <row r="8">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | (M*=(), A*=(0,))</t>
+          <t>(M=(), A=(11,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.1692117750644684</v>
+        <v>0.002759456634521484</v>
       </c>
       <c r="L8" t="n">
-        <v>8.7531</v>
+        <v>1.6524</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="U8" t="n">
-        <v>8.367800000000001</v>
+        <v>3.3752</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="AD8" t="n">
-        <v>10.306</v>
+        <v>4.8931</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="AM8" t="n">
-        <v>10.3005</v>
+        <v>8.303599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -8746,7 +8746,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.4719</v>
+        <v>1.2152</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>4.6905</v>
+        <v>4.2158</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.988</v>
+        <v>7.4051</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.0731</v>
+        <v>5.7027</v>
       </c>
     </row>
     <row r="10">
@@ -8883,14 +8883,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | (M*=(), A*=(2,))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.02445322275161743</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L10" t="n">
-        <v>0.416</v>
+        <v>0.4284</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8916,14 +8916,14 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="U10" t="n">
-        <v>0.77</v>
+        <v>1.6099</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8949,14 +8949,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5022</v>
+        <v>6.6026</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>0.02445322275161743</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.898</v>
+        <v>2.7199</v>
       </c>
     </row>
     <row r="11">
@@ -9027,14 +9027,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(M=(), A=(13,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14))</t>
+          <t>(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | (M*=(), A*=(5,))</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1266</v>
+        <v>0.2918</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9060,14 +9060,14 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1701</v>
+        <v>1.6688</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -9093,14 +9093,14 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2019</v>
+        <v>4.6013</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3636</v>
+        <v>3.5022</v>
       </c>
     </row>
     <row r="12">
@@ -9171,14 +9171,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>(M=(), A=(2,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
+          <t>(M=(), A=(5,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.006561070680618286</v>
+        <v>0.0005945563316345215</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0975</v>
+        <v>0.2204</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9204,14 +9204,14 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>0.01078173518180847</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2315</v>
+        <v>1.6569</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>0.01078173518180847</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2404</v>
+        <v>3.4562</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9270,14 +9270,14 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="AL12" t="n">
-        <v>0.008752733469009399</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5794</v>
+        <v>2.7812</v>
       </c>
     </row>
     <row r="13">
@@ -9315,14 +9315,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(6,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.4428481459617615</v>
+        <v>0.01416301727294922</v>
       </c>
       <c r="L13" t="n">
-        <v>15.536</v>
+        <v>3.6999</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9348,14 +9348,14 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>2.437360763549805</v>
+        <v>1.829068303108215</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3677</v>
+        <v>6.7355</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9381,14 +9381,14 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13)) | G1(M=(8,), A=(8,))</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>2.437360763549805</v>
+        <v>2.223263263702393</v>
       </c>
       <c r="AD13" t="n">
-        <v>15.6785</v>
+        <v>8.807600000000001</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -9414,14 +9414,14 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL13" t="n">
-        <v>2.437360763549805</v>
+        <v>1.829068303108215</v>
       </c>
       <c r="AM13" t="n">
-        <v>17.5909</v>
+        <v>13.4587</v>
       </c>
     </row>
     <row r="14">
@@ -9459,14 +9459,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>(M=(), A=(11,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(5,))</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.05629348754882812</v>
+        <v>0.05528867244720459</v>
       </c>
       <c r="L14" t="n">
-        <v>7.2606</v>
+        <v>1.5615</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9492,14 +9492,14 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(12,), A=(12,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1.757790565490723</v>
+        <v>1.250390529632568</v>
       </c>
       <c r="U14" t="n">
-        <v>6.3993</v>
+        <v>4.4984</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9525,14 +9525,14 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>1.376205682754517</v>
+        <v>1.250390529632568</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5636</v>
+        <v>4.6283</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -9558,14 +9558,14 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AL14" t="n">
-        <v>1.376205682754517</v>
+        <v>1.250390529632568</v>
       </c>
       <c r="AM14" t="n">
-        <v>8.6837</v>
+        <v>6.7308</v>
       </c>
     </row>
     <row r="15">
@@ -9603,14 +9603,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>(M=(), A=(0,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13))</t>
+          <t>(M=(), A=(11,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.1692117750644684</v>
+        <v>0.002759456634521484</v>
       </c>
       <c r="L15" t="n">
-        <v>11.3338</v>
+        <v>1.6408</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="U15" t="n">
-        <v>8.8301</v>
+        <v>3.1448</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="AD15" t="n">
-        <v>7.7549</v>
+        <v>6.9767</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>0.1692117750644684</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.7721</v>
+        <v>9.227</v>
       </c>
     </row>
     <row r="16">
@@ -9747,14 +9747,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>(M=(), A=(12,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13))</t>
+          <t>(M=(), A=(7,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.1572507619857788</v>
+        <v>0.007079154253005981</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7273</v>
+        <v>0.8255</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9891,14 +9891,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | (M*=(), A*=(11,))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L17" t="n">
-        <v>0.717</v>
+        <v>0.4022</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9924,14 +9924,14 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7979000000000001</v>
+        <v>2.582</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9957,14 +9957,14 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8332000000000001</v>
+        <v>3.719</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -9990,14 +9990,14 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AL17" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.9032</v>
+        <v>2.3047</v>
       </c>
     </row>
     <row r="18">
@@ -10035,14 +10035,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>(M=(), A=(13,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2418</v>
+        <v>0.4185</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10068,14 +10068,14 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1684</v>
+        <v>1.7806</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -10101,14 +10101,14 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2885</v>
+        <v>2.1912</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.3252</v>
+        <v>4.2359</v>
       </c>
     </row>
     <row r="19">
@@ -10179,14 +10179,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13)) | (M*=(), A*=(8,))</t>
+          <t>(M=(), A=(5,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.001939654350280762</v>
+        <v>0.0005945563316345215</v>
       </c>
       <c r="L19" t="n">
-        <v>0.316</v>
+        <v>0.5994</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10212,14 +10212,14 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(), A=(12,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>0.02076083421707153</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2883</v>
+        <v>1.9475</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -10245,14 +10245,14 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(6,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>0.01112627983093262</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.2718</v>
+        <v>3.1632</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>0.001939654350280762</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.3737</v>
+        <v>4.6884</v>
       </c>
     </row>
     <row r="20">
@@ -10323,14 +10323,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.4428481459617615</v>
+        <v>0.01416301727294922</v>
       </c>
       <c r="L20" t="n">
-        <v>18.3183</v>
+        <v>5.0983</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -10356,14 +10356,14 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(4,), A=(4,))</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>2.206778764724731</v>
+        <v>2.133479356765747</v>
       </c>
       <c r="U20" t="n">
-        <v>17.3201</v>
+        <v>9.8582</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -10389,14 +10389,14 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(4,), A=(4,))</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>2.206778764724731</v>
+        <v>2.133479356765747</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.6627</v>
+        <v>10.2212</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -10422,14 +10422,14 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL20" t="n">
-        <v>2.206778764724731</v>
+        <v>1.886789083480835</v>
       </c>
       <c r="AM20" t="n">
-        <v>17.1678</v>
+        <v>10.8691</v>
       </c>
     </row>
     <row r="21">
@@ -10467,14 +10467,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(14,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.07223978638648987</v>
+        <v>0.05528867244720459</v>
       </c>
       <c r="L21" t="n">
-        <v>9.9587</v>
+        <v>2.418</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="U21" t="n">
-        <v>9.1549</v>
+        <v>4.1788</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AD21" t="n">
-        <v>8.6645</v>
+        <v>6.398</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AM21" t="n">
-        <v>7.4576</v>
+        <v>6.4335</v>
       </c>
     </row>
     <row r="22">
@@ -10618,7 +10618,7 @@
         <v>0.002759456634521484</v>
       </c>
       <c r="L22" t="n">
-        <v>10.6571</v>
+        <v>2.7642</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -10644,14 +10644,14 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(6,), A=(6,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>1.330678820610046</v>
+        <v>1.269968748092651</v>
       </c>
       <c r="U22" t="n">
-        <v>9.870900000000001</v>
+        <v>4.7563</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -10677,14 +10677,14 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(6,), A=(6,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>1.330678820610046</v>
+        <v>1.269968748092651</v>
       </c>
       <c r="AD22" t="n">
-        <v>7.5504</v>
+        <v>6.5151</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -10710,14 +10710,14 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 14)) | G1(M=(10,), A=(10,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL22" t="n">
-        <v>1.634117960929871</v>
+        <v>1.269968748092651</v>
       </c>
       <c r="AM22" t="n">
-        <v>7.281</v>
+        <v>7.6802</v>
       </c>
     </row>
     <row r="23">
@@ -10762,7 +10762,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>3.908</v>
+        <v>1.5036</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="U23" t="n">
-        <v>5.2961</v>
+        <v>3.4154</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.7605</v>
+        <v>4.438</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -10854,14 +10854,14 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12)) | G1(M=(10,), A=(10,)) | G2(M=(13,), A=(13,)) | G3(M=(), A=(14,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
         </is>
       </c>
       <c r="AL23" t="n">
-        <v>1.18786609172821</v>
+        <v>2.205371856689453e-05</v>
       </c>
       <c r="AM23" t="n">
-        <v>4.9352</v>
+        <v>5.8697</v>
       </c>
     </row>
     <row r="24">
@@ -10899,14 +10899,14 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>(M=(), A=(2,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.02445322275161743</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4108</v>
+        <v>0.6106</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -10932,14 +10932,14 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3454</v>
+        <v>1.7873</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -10965,14 +10965,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.3845</v>
+        <v>2.5711</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>0.02445322275161743</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.4487</v>
+        <v>2.2425</v>
       </c>
     </row>
     <row r="25">
@@ -11043,14 +11043,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14)) | (M*=(), A*=(13,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="L25" t="n">
-        <v>0.141</v>
+        <v>0.5169</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -11076,14 +11076,14 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1824</v>
+        <v>1.3509</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -11109,14 +11109,14 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.2226</v>
+        <v>1.7277</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.315</v>
+        <v>3.3319</v>
       </c>
     </row>
     <row r="26">
@@ -11187,14 +11187,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | (M*=(), A*=(8,))</t>
+          <t>(M=(), A=(5,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14))</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.001939654350280762</v>
+        <v>0.0005945563316345215</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2006</v>
+        <v>0.4875</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -11220,14 +11220,14 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>0.01078173518180847</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1596</v>
+        <v>1.6215</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -11253,14 +11253,14 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>0.01078173518180847</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.2344</v>
+        <v>2.5974</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>0.001939654350280762</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.2727</v>
+        <v>3.987</v>
       </c>
     </row>
     <row r="27">
@@ -11331,14 +11331,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(4,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.03294903039932251</v>
+        <v>0.01416301727294922</v>
       </c>
       <c r="L27" t="n">
-        <v>21.6905</v>
+        <v>4.7878</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -11364,14 +11364,14 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(4,), A=(4,))</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>2.052023649215698</v>
+        <v>2.00212025642395</v>
       </c>
       <c r="U27" t="n">
-        <v>20.571</v>
+        <v>7.4137</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -11397,14 +11397,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(4,), A=(4,))</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>2.052023649215698</v>
+        <v>2.00212025642395</v>
       </c>
       <c r="AD27" t="n">
-        <v>14.7709</v>
+        <v>8.8569</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -11430,14 +11430,14 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL27" t="n">
-        <v>2.052023649215698</v>
+        <v>1.721155524253845</v>
       </c>
       <c r="AM27" t="n">
-        <v>15.0155</v>
+        <v>11.872</v>
       </c>
     </row>
     <row r="28">
@@ -11475,14 +11475,14 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>(M=(), A=(11,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | (M*=(), A*=(5,))</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.05629348754882812</v>
+        <v>0.05528867244720459</v>
       </c>
       <c r="L28" t="n">
-        <v>9.9582</v>
+        <v>2.1605</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -11508,14 +11508,14 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(12,), A=(12,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>1.746455192565918</v>
+        <v>1.243469953536987</v>
       </c>
       <c r="U28" t="n">
-        <v>8.232699999999999</v>
+        <v>4.4224</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -11541,14 +11541,14 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>1.349055528640747</v>
+        <v>1.243469953536987</v>
       </c>
       <c r="AD28" t="n">
-        <v>8.7638</v>
+        <v>8.513299999999999</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -11574,14 +11574,14 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(2,), A=(2,))</t>
         </is>
       </c>
       <c r="AL28" t="n">
-        <v>1.349055528640747</v>
+        <v>1.243469953536987</v>
       </c>
       <c r="AM28" t="n">
-        <v>8.4824</v>
+        <v>7.1754</v>
       </c>
     </row>
     <row r="29">
@@ -11626,7 +11626,7 @@
         <v>0.002759456634521484</v>
       </c>
       <c r="L29" t="n">
-        <v>9.3596</v>
+        <v>2.2744</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>1.193038702011108</v>
       </c>
       <c r="U29" t="n">
-        <v>9.529500000000001</v>
+        <v>4.8262</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -11685,14 +11685,14 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(6,), A=(6,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AC29" t="n">
-        <v>1.215973019599915</v>
+        <v>1.193038702011108</v>
       </c>
       <c r="AD29" t="n">
-        <v>9.312799999999999</v>
+        <v>4.802</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -11718,14 +11718,14 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13)) | G1(M=(10,), A=(10,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL29" t="n">
-        <v>1.632424592971802</v>
+        <v>1.193038702011108</v>
       </c>
       <c r="AM29" t="n">
-        <v>9.4811</v>
+        <v>9.897</v>
       </c>
     </row>
     <row r="30">
@@ -11763,14 +11763,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>(M=(), A=(12,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13))</t>
+          <t>(M=(), A=(7,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.1572507619857788</v>
+        <v>0.007079154253005981</v>
       </c>
       <c r="L30" t="n">
-        <v>3.1481</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -11796,14 +11796,14 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12)) | G1(M=(10,), A=(10,)) | G2(M=(13,), A=(13,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="T30" t="n">
-        <v>1.187844038009644</v>
+        <v>0.7213985919952393</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1288</v>
+        <v>2.2514</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -11829,14 +11829,14 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(12,), A=(12,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>1.04074227809906</v>
+        <v>0.7213985919952393</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.9211</v>
+        <v>2.7237</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -11862,14 +11862,14 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(12,), A=(12,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="AL30" t="n">
-        <v>1.04074227809906</v>
+        <v>0.7213985919952393</v>
       </c>
       <c r="AM30" t="n">
-        <v>2.965</v>
+        <v>5.649</v>
       </c>
     </row>
     <row r="31">
@@ -11907,14 +11907,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>(M=(), A=(11,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4034</v>
+        <v>0.3826</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -11940,14 +11940,14 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="U31" t="n">
-        <v>0.358</v>
+        <v>1.357</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -11973,14 +11973,14 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.4773</v>
+        <v>2.4087</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -12006,14 +12006,14 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13)) | G1(M=(), A=(11,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AL31" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.51</v>
+        <v>2.6905</v>
       </c>
     </row>
     <row r="32">
@@ -12051,14 +12051,14 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12)) | (M*=(), A*=(13,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1391</v>
+        <v>0.3239</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -12084,14 +12084,14 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1509</v>
+        <v>1.0214</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -12117,14 +12117,14 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12)) | G1(M=(), A=(13,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13)) | G1(M=(), A=(5,))</t>
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.1967</v>
+        <v>1.5639</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.3333</v>
+        <v>3.3309</v>
       </c>
     </row>
     <row r="33">
@@ -12195,14 +12195,14 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>(M=(), A=(8,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13))</t>
+          <t>(M=(), A=(5,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13))</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.001939654350280762</v>
+        <v>0.0005945563316345215</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2302</v>
+        <v>0.4405</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -12228,14 +12228,14 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13)) | G1(M=(), A=(12,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T33" t="n">
-        <v>0.02076083421707153</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2354</v>
+        <v>1.4159</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>0.001939654350280762</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.3163</v>
+        <v>1.7292</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>0.001939654350280762</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.3754</v>
+        <v>2.9269</v>
       </c>
     </row>
     <row r="34">
@@ -12346,7 +12346,7 @@
         <v>0.03294903039932251</v>
       </c>
       <c r="L34" t="n">
-        <v>12.8188</v>
+        <v>3.1687</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -12372,14 +12372,14 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(8,), A=())</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>1.74397075176239</v>
+        <v>1.593281269073486</v>
       </c>
       <c r="U34" t="n">
-        <v>12.0065</v>
+        <v>5.5014</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>1.09422767162323</v>
       </c>
       <c r="AD34" t="n">
-        <v>11.3782</v>
+        <v>8.5276</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>1.09422767162323</v>
       </c>
       <c r="AM34" t="n">
-        <v>11.3691</v>
+        <v>8.530200000000001</v>
       </c>
     </row>
     <row r="35">
@@ -12483,14 +12483,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 3, 4, 6, 7, 9, 10, 12, 13)) | (M*=(), A*=(1,))</t>
+          <t>(M=(), A=(1,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="K35" t="n">
         <v>0.0559191107749939</v>
       </c>
       <c r="L35" t="n">
-        <v>6.397</v>
+        <v>1.5894</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>0.9290870428085327</v>
       </c>
       <c r="U35" t="n">
-        <v>5.131</v>
+        <v>2.6</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -12549,14 +12549,14 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(11,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(2,), A=())</t>
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>0.9290870428085327</v>
+        <v>0.7864952087402344</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.1615</v>
+        <v>3.551</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -12582,14 +12582,14 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(11,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(2,), A=())</t>
         </is>
       </c>
       <c r="AL35" t="n">
-        <v>0.9290870428085327</v>
+        <v>0.7864952087402344</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.2693</v>
+        <v>4.6393</v>
       </c>
     </row>
     <row r="36">
@@ -12627,14 +12627,14 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 1, 3, 4, 6, 7, 9, 10, 13)) | (M*=(), A*=(12,))</t>
+          <t>(M=(), A=(10,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 1, 3, 4, 6, 7, 9, 12, 13))</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.0181734561920166</v>
+        <v>0.007182478904724121</v>
       </c>
       <c r="L36" t="n">
-        <v>6.7541</v>
+        <v>1.6024</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -12660,14 +12660,14 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 4, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 1, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(3,), A=(3,)) | G2(M=(5,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="T36" t="n">
-        <v>1.043848872184753</v>
+        <v>0.1692117750644684</v>
       </c>
       <c r="U36" t="n">
-        <v>5.7308</v>
+        <v>3.3277</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -12693,14 +12693,14 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(11,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>0.9244636297225952</v>
+        <v>0.1692117750644684</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.1014</v>
+        <v>4.4012</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -12726,14 +12726,14 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13)) | G1(M=(11,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="AL36" t="n">
-        <v>0.9244636297225952</v>
+        <v>0.1692117750644684</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.2304</v>
+        <v>5.6448</v>
       </c>
     </row>
     <row r="37">
@@ -12771,14 +12771,14 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>(M=(), A=(1,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 3, 4, 6, 7, 9, 10, 12, 13))</t>
+          <t>(M=(), A=(7,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 1, 3, 4, 6, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.09668245911598206</v>
+        <v>0.007079154253005981</v>
       </c>
       <c r="L37" t="n">
-        <v>3.2549</v>
+        <v>0.9683</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>0.04210850596427917</v>
       </c>
       <c r="U37" t="n">
-        <v>2.7962</v>
+        <v>13.4818</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>0.04210850596427917</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.615</v>
+        <v>12.318</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>0.04210850596427917</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.8447</v>
+        <v>14.6823</v>
       </c>
     </row>
     <row r="38">
@@ -12915,14 +12915,14 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 12)) | (M*=(), A*=(13,))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(0, 1, 3, 4, 6, 7, 9, 12, 13))</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.01865449547767639</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4592</v>
+        <v>0.4419</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>0.1741378605365753</v>
       </c>
       <c r="U38" t="n">
-        <v>0.482</v>
+        <v>0.6518</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>0.1741378605365753</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.6797</v>
+        <v>1.3662</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>0.1741378605365753</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.5262</v>
+        <v>1.5928</v>
       </c>
     </row>
     <row r="39">
@@ -13066,7 +13066,7 @@
         <v>0.001649767160415649</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2035</v>
+        <v>0.4503</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>0.001649767160415649</v>
       </c>
       <c r="U39" t="n">
-        <v>0.1395</v>
+        <v>0.9536</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>0.001649767160415649</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.1666</v>
+        <v>1.7038</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>0.001649767160415649</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.207</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="40">
@@ -13203,14 +13203,14 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>(M=(), A=(6,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 1, 3, 4, 7, 9, 10, 12, 13))</t>
+          <t>(M=(), A=(13,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 1, 3, 4, 6, 7, 9, 10, 12))</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.01112627983093262</v>
+        <v>0.004612058401107788</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1211</v>
+        <v>0.3587</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -13236,14 +13236,14 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 3, 4, 6, 7, 9, 10, 13)) | G1(M=(), A=(12,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="T40" t="n">
-        <v>0.02076083421707153</v>
+        <v>0.008752733469009399</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1388</v>
+        <v>0.823</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -13269,14 +13269,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 3, 4, 7, 9, 10, 12, 13)) | G1(M=(), A=(6,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>0.01112627983093262</v>
+        <v>0.008752733469009399</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.1599</v>
+        <v>1.6483</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -13302,14 +13302,14 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 1, 3, 4, 7, 9, 10, 12, 13)) | G1(M=(), A=(6,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(1, 3, 4, 6, 7, 9, 10, 12, 13))</t>
         </is>
       </c>
       <c r="AL40" t="n">
-        <v>0.01112627983093262</v>
+        <v>0.008752733469009399</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.1915</v>
+        <v>2.7529</v>
       </c>
     </row>
     <row r="41">
@@ -13354,7 +13354,7 @@
         <v>0.03294903039932251</v>
       </c>
       <c r="L41" t="n">
-        <v>10.2193</v>
+        <v>3.5866</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -13380,14 +13380,14 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(14,), A=(14,))</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 2, 4, 6, 8, 10, 12, 14)) | G1(M=(11,), A=())</t>
         </is>
       </c>
       <c r="T41" t="n">
-        <v>1.266045212745667</v>
+        <v>0.7795747518539429</v>
       </c>
       <c r="U41" t="n">
-        <v>9.0106</v>
+        <v>7.4745</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -13413,14 +13413,14 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 2, 4, 6, 8, 10, 12, 14)) | G1(M=(1,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 2, 4, 6, 8, 10, 12, 14)) | G1(M=(11,), A=())</t>
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>1.681207895278931</v>
+        <v>0.7795747518539429</v>
       </c>
       <c r="AD41" t="n">
-        <v>9.3446</v>
+        <v>7.0012</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -13446,14 +13446,14 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 2, 4, 6, 8, 10, 12, 14)) | G1(M=(3,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(0, 2, 4, 6, 8, 10, 12, 14)) | G1(M=(11,), A=())</t>
         </is>
       </c>
       <c r="AL41" t="n">
-        <v>1.611556053161621</v>
+        <v>0.7795747518539429</v>
       </c>
       <c r="AM41" t="n">
-        <v>9.374000000000001</v>
+        <v>9.6089</v>
       </c>
     </row>
     <row r="42">
@@ -13491,14 +13491,14 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>(M=(), A=(4,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 2, 6, 8, 10, 12, 14))</t>
+          <t>(M=(), A=(14,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 2, 4, 6, 8, 10, 12))</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.13511061668396</v>
+        <v>0.07223978638648987</v>
       </c>
       <c r="L42" t="n">
-        <v>6.2152</v>
+        <v>1.6369</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="U42" t="n">
-        <v>5.7882</v>
+        <v>2.4737</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.2337</v>
+        <v>4.2781</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>0.07223978638648987</v>
       </c>
       <c r="AM42" t="n">
-        <v>4.8154</v>
+        <v>6.2966</v>
       </c>
     </row>
     <row r="43">
@@ -13635,14 +13635,14 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(0, 2, 4, 6, 8, 12, 14)) | (M*=(), A*=(10,))</t>
+          <t>(M=(), A=(10,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(0, 2, 4, 6, 8, 12, 14))</t>
         </is>
       </c>
       <c r="K43" t="n">
         <v>0.007182478904724121</v>
       </c>
       <c r="L43" t="n">
-        <v>6.1115</v>
+        <v>2.2205</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -13668,14 +13668,14 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>G0(M=(2, 3, 4, 6, 9, 10, 11, 12, 14), A=(0, 2, 4, 6, 10, 12, 14)) | G1(M=(1, 5), A=()) | G2(M=(7, 8, 13), A=(8,))</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(4, 6, 8, 10, 12, 14)) | G2(M=(2, 11), A=(2,))</t>
         </is>
       </c>
       <c r="T43" t="n">
-        <v>0.8141067028045654</v>
+        <v>0.4363062381744385</v>
       </c>
       <c r="U43" t="n">
-        <v>4.8003</v>
+        <v>3.2909</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -13701,14 +13701,14 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>G0(M=(2, 3, 4, 6, 9, 10, 11, 12, 14), A=(0, 2, 4, 6, 10, 12, 14)) | G1(M=(1, 13), A=()) | G2(M=(5, 8), A=(8,)) | G3(M=(7,), A=())</t>
+          <t>G0(M=(2, 3, 4, 5, 6, 7, 8, 9, 11, 12, 13), A=(0, 2, 4, 6, 8, 12)) | G1(M=(1, 10, 14), A=(10, 14))</t>
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>0.813872218132019</v>
+        <v>0.6424335241317749</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.0413</v>
+        <v>4.4114</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -13734,14 +13734,14 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>G0(M=(4, 5, 6, 8, 9, 10, 12, 14), A=(0, 4, 6, 8, 10, 12, 14)) | G1(M=(1,), A=()) | G2(M=(2, 3, 11, 13), A=(2,)) | G3(M=(7,), A=())</t>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(4, 6, 8, 10, 12, 14)) | G2(M=(2, 11), A=(2,))</t>
         </is>
       </c>
       <c r="AL43" t="n">
-        <v>0.7674528956413269</v>
+        <v>0.4363062381744385</v>
       </c>
       <c r="AM43" t="n">
-        <v>4.8537</v>
+        <v>5.6461</v>
       </c>
     </row>
     <row r="44">
@@ -13779,14 +13779,14 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>(M=(), A=(4,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 2, 6, 8, 10, 12, 14))</t>
+          <t>(M=(), A=(14,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(0, 2, 4, 6, 8, 10, 12))</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.1677759289741516</v>
+        <v>2.205371856689453e-05</v>
       </c>
       <c r="L44" t="n">
-        <v>2.8297</v>
+        <v>1.1879</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -13812,14 +13812,14 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(2, 4, 6, 8, 10, 12, 14))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(), A=(14,))</t>
         </is>
       </c>
       <c r="T44" t="n">
-        <v>0.04210850596427917</v>
+        <v>2.205371856689453e-05</v>
       </c>
       <c r="U44" t="n">
-        <v>2.8842</v>
+        <v>2.0461</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.9708</v>
+        <v>4.3379</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>2.205371856689453e-05</v>
       </c>
       <c r="AM44" t="n">
-        <v>3.1202</v>
+        <v>4.9404</v>
       </c>
     </row>
     <row r="45">
@@ -13923,14 +13923,14 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | (M*=(), A*=(14,))</t>
+          <t>(M=(), A=(10,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(0, 2, 4, 6, 8, 12, 14))</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.001727968454360962</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3176</v>
+        <v>0.3877</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -13956,14 +13956,14 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 4, 6, 8, 10, 12, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T45" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="U45" t="n">
-        <v>0.2544</v>
+        <v>0.6964</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -13989,14 +13989,14 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 4, 6, 8, 10, 12, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.2717</v>
+        <v>1.3819</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -14022,14 +14022,14 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(0, 4, 6, 8, 10, 12, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AL45" t="n">
-        <v>0.04920902848243713</v>
+        <v>0.02445322275161743</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.3481</v>
+        <v>2.1349</v>
       </c>
     </row>
     <row r="46">
@@ -14074,7 +14074,7 @@
         <v>0.001735150814056396</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1379</v>
+        <v>0.2156</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>0.09815007448196411</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1313</v>
+        <v>0.2973</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>0.09815007448196411</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.139</v>
+        <v>0.4296</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -14166,14 +14166,14 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>G0(M=(0, 2, 4, 6, 10), A=(0, 2, 4, 6, 10)) | G1(M=(8, 14), A=(8, 14)) | G2(M=(12,), A=(12,))</t>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 14), A=(0, 2, 4, 6, 8, 10, 14)) | G1(M=(12,), A=(12,))</t>
         </is>
       </c>
       <c r="AL46" t="n">
-        <v>0.1146263182163239</v>
+        <v>0.09815007448196411</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.1381</v>
+        <v>0.4399</v>
       </c>
     </row>
     <row r="47">
@@ -14211,14 +14211,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>(M=(), A=(2,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(0, 4, 6, 8, 10, 12, 14))</t>
+          <t>(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 2, 4, 6, 10, 12, 14)) | (M*=(), A*=(8,))</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.006561070680618286</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="L47" t="n">
-        <v>0.0999</v>
+        <v>0.3495</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -14244,14 +14244,14 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(2, 4, 6, 8, 10, 12, 14))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 2, 4, 6, 10, 12, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="T47" t="n">
-        <v>0.008752733469009399</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="U47" t="n">
-        <v>0.1235</v>
+        <v>1.1565</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -14277,14 +14277,14 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 2, 4, 6, 8, 10, 12)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 4, 6, 8, 10, 12, 14)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>0.01078173518180847</v>
+        <v>0.006561070680618286</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.1377</v>
+        <v>2.5703</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -14310,14 +14310,14 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>G0(M=(), A=(0,)) | G1(M=(1, 3, 5, 7, 9, 11, 13), A=(2, 4, 6, 8, 10, 12, 14))</t>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13), A=(0, 2, 4, 6, 10, 12, 14)) | G1(M=(), A=(8,))</t>
         </is>
       </c>
       <c r="AL47" t="n">
-        <v>0.008752733469009399</v>
+        <v>0.001939654350280762</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.1324</v>
+        <v>3.2902</v>
       </c>
     </row>
     <row r="48">
@@ -14355,14 +14355,14 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A*=(1, 3, 7, 9, 11, 13))</t>
+          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 3, 7, 9, 11, 13)) | (M*=(), A*=(5,))</t>
         </is>
       </c>
       <c r="K48" t="n">
         <v>0.01416301727294922</v>
       </c>
       <c r="L48" t="n">
-        <v>9.5855</v>
+        <v>3.0154</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -14388,14 +14388,14 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(8,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(4,), A=())</t>
         </is>
       </c>
       <c r="T48" t="n">
-        <v>1.048153638839722</v>
+        <v>0.5149270296096802</v>
       </c>
       <c r="U48" t="n">
-        <v>9.143800000000001</v>
+        <v>9.023400000000001</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>0.5149270296096802</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.9865</v>
+        <v>7.8202</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>0.5149270296096802</v>
       </c>
       <c r="AM48" t="n">
-        <v>6.6689</v>
+        <v>8.6607</v>
       </c>
     </row>
     <row r="49">
@@ -14499,14 +14499,14 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 5, 7, 9, 11, 13)) | (M*=(), A*=(3,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 3, 7, 9, 11, 13))</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.1285316944122314</v>
+        <v>0.05528867244720459</v>
       </c>
       <c r="L49" t="n">
-        <v>4.8585</v>
+        <v>1.4261</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -14532,14 +14532,14 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(12,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 7, 9, 11, 13)) | G1(M=(5,), A=(5,))</t>
         </is>
       </c>
       <c r="T49" t="n">
-        <v>0.5587359666824341</v>
+        <v>0.5196987390518188</v>
       </c>
       <c r="U49" t="n">
-        <v>4.635</v>
+        <v>2.8771</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -14565,14 +14565,14 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(12,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 7, 9, 11, 13)) | G1(M=(5,), A=(5,))</t>
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>0.5587359666824341</v>
+        <v>0.5196987390518188</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.8646</v>
+        <v>3.8841</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -14598,14 +14598,14 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(12,), A=())</t>
+          <t>G0(M=(0, 1, 2, 3, 4, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 7, 9, 11, 13)) | G1(M=(5,), A=(5,))</t>
         </is>
       </c>
       <c r="AL49" t="n">
-        <v>0.5587359666824341</v>
+        <v>0.5196987390518188</v>
       </c>
       <c r="AM49" t="n">
-        <v>3.7314</v>
+        <v>5.9169</v>
       </c>
     </row>
     <row r="50">
@@ -14650,7 +14650,7 @@
         <v>0.002759456634521484</v>
       </c>
       <c r="L50" t="n">
-        <v>4.0668</v>
+        <v>1.5622</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14676,14 +14676,14 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14), A=(1, 3, 5, 7, 11, 13)) | G1(M=(9,), A=(9,))</t>
         </is>
       </c>
       <c r="T50" t="n">
-        <v>0.8650623559951782</v>
+        <v>0.6176963448524475</v>
       </c>
       <c r="U50" t="n">
-        <v>4.6677</v>
+        <v>2.2446</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14709,14 +14709,14 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(14,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14), A=(1, 3, 5, 7, 11, 13)) | G1(M=(9,), A=(9,))</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>0.8650623559951782</v>
+        <v>0.6176963448524475</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.3197</v>
+        <v>5.2762</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>0.6176963448524475</v>
       </c>
       <c r="AM50" t="n">
-        <v>3.8255</v>
+        <v>5.5153</v>
       </c>
     </row>
     <row r="51">
@@ -14787,14 +14787,14 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 9, 11, 13)) | (M*=(), A*=(7,))</t>
+          <t>(M=(), A=(7,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A*=(1, 3, 5, 9, 11, 13))</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>0.007079154253005981</v>
       </c>
       <c r="L51" t="n">
-        <v>1.3792</v>
+        <v>0.9746</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14820,14 +14820,14 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(12,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 9, 11, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="T51" t="n">
-        <v>0.4521380662918091</v>
+        <v>0.312005341053009</v>
       </c>
       <c r="U51" t="n">
-        <v>1.4567</v>
+        <v>1.2808</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14853,14 +14853,14 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(2,), A=())</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 9, 11, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>0.4076170921325684</v>
+        <v>0.312005341053009</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.4455</v>
+        <v>1.7391</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -14886,14 +14886,14 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 4, 5, 7, 9, 11), A=(1, 3, 5, 7, 9, 11)) | G1(M=(2, 6, 8, 10, 12, 13), A=(13,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13), A=(1, 3, 5, 9, 11, 13)) | G1(M=(7,), A=(7,))</t>
         </is>
       </c>
       <c r="AL51" t="n">
-        <v>0.7796415090560913</v>
+        <v>0.312005341053009</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.4365</v>
+        <v>4.1018</v>
       </c>
     </row>
     <row r="52">
@@ -14931,14 +14931,14 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>(M=(), A=(11,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(1, 3, 5, 7, 9, 13))</t>
+          <t>(M=(), A=(1,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A*=(3, 5, 7, 9, 11, 13))</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.03601160645484924</v>
+        <v>0.002572149038314819</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2696</v>
+        <v>0.5275</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14964,14 +14964,14 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 12, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(10,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 5, 7, 9, 13)) | G1(M=(), A=(11,))</t>
         </is>
       </c>
       <c r="T52" t="n">
-        <v>0.1314705908298492</v>
+        <v>0.03601160645484924</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1782</v>
+        <v>1.146</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14997,14 +14997,14 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 12, 13), A=(1, 3, 5, 7, 9, 11, 13)) | G1(M=(10,), A=())</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13), A=(1, 3, 5, 7, 9, 13)) | G1(M=(), A=(11,))</t>
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>0.1314705908298492</v>
+        <v>0.03601160645484924</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.1817</v>
+        <v>0.9043</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>0.03601160645484924</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.2086</v>
+        <v>1.0968</v>
       </c>
     </row>
     <row r="53">
@@ -15075,14 +15075,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>(M=(0, 2, 4, 6, 8, 10, 12, 14), A=(1, 3, 5, 7, 9, 11)) | (M*=(), A*=(13,))</t>
+          <t>(M=(), A=(5,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14), A*=(1, 3, 7, 9, 11, 13))</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.001649767160415649</v>
+        <v>0.001028925180435181</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0683</v>
+        <v>0.3645</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="U53" t="n">
-        <v>0.09909999999999999</v>
+        <v>1.5328</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.128</v>
+        <v>1.9042</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>0.001028925180435181</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.188</v>
+        <v>3.7819</v>
       </c>
     </row>
     <row r="54">
@@ -15219,14 +15219,14 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>(M=(), A=(1,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(3, 5, 7, 9, 11, 13))</t>
+          <t>(M=(), A=(5,)) | (M*=(1, 3, 5, 7, 9, 11, 13), A*=(1, 3, 7, 9, 11, 13))</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.0144655704498291</v>
+        <v>0.0005945563316345215</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0649</v>
+        <v>0.1299</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15252,14 +15252,14 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 7, 9, 11, 13), A=(1, 3, 7, 9, 11, 13)) | G1(M=(5,), A=(5,))</t>
+          <t>G0(M=(1, 5, 7, 9, 11, 13), A=(1, 5, 7, 9, 11, 13)) | G1(M=(3,), A=(3,))</t>
         </is>
       </c>
       <c r="T54" t="n">
-        <v>0.06063783168792725</v>
+        <v>0.04094809293746948</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0559</v>
+        <v>0.3067</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15285,14 +15285,14 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>G0(M=(1, 3, 5, 7, 9, 13), A=(1, 3, 5, 7, 9, 13)) | G1(M=(11,), A=(11,))</t>
+          <t>G0(M=(1, 5, 7, 9, 11, 13), A=(1, 5, 7, 9, 11, 13)) | G1(M=(3,), A=(3,))</t>
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>0.06462672352790833</v>
+        <v>0.04094809293746948</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2723</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>0.04094809293746948</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.082</v>
+        <v>0.3007</v>
       </c>
     </row>
     <row r="55">
@@ -15370,7 +15370,7 @@
         <v>0.002759456634521484</v>
       </c>
       <c r="L55" t="n">
-        <v>5.1522</v>
+        <v>2.3417</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15396,14 +15396,14 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 13, 14), A=(1, 2, 3, 4, 5, 6, 9, 10, 11, 13, 14)) | G1(M=(8, 12), A=(12,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="T55" t="n">
-        <v>1.274153470993042</v>
+        <v>1.059518337249756</v>
       </c>
       <c r="U55" t="n">
-        <v>4.6605</v>
+        <v>3.9992</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15429,14 +15429,14 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14), A=(1, 2, 3, 4, 5, 9, 10, 11, 12, 13, 14)) | G1(M=(6,), A=(6,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>1.226643800735474</v>
+        <v>1.059518337249756</v>
       </c>
       <c r="AD55" t="n">
-        <v>5.0046</v>
+        <v>4.6944</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -15462,14 +15462,14 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 13, 14), A=(1, 2, 3, 4, 5, 6, 9, 10, 11, 13, 14)) | G1(M=(8, 12), A=(12,))</t>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14), A=(1, 2, 3, 4, 5, 6, 9, 10, 12, 13, 14)) | G1(M=(11,), A=(11,))</t>
         </is>
       </c>
       <c r="AL55" t="n">
-        <v>1.274153470993042</v>
+        <v>1.059518337249756</v>
       </c>
       <c r="AM55" t="n">
-        <v>4.7524</v>
+        <v>7.7975</v>
       </c>
     </row>
   </sheetData>
@@ -15479,12 +15479,12 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="M3:U3"/>
     <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="V3:AD3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="AB4:AD4"/>
     <mergeCell ref="P4:R4"/>
@@ -15882,6 +15882,17 @@
       <c r="F6" t="n">
         <v>26899.5513</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>(M=(), A=(17,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 18, 19))</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02363294363021851</v>
+      </c>
+      <c r="L6" t="n">
+        <v>237.7809</v>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19)) | G1(M=(), A=(16,))</t>
@@ -15893,6 +15904,17 @@
       <c r="O6" t="n">
         <v>5432.8747</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(1,), A=(1,))</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>2.628543615341187</v>
+      </c>
+      <c r="U6" t="n">
+        <v>713.8187</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>G0(M=(0,), A=(0, 4, 10, 11)) | G1(M=(1, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14, 15, 16, 17, 18, 19), A=(1, 2, 3, 5, 8, 13, 14, 15, 16, 17, 18)) | G2(M=(2, 11), A=(6, 9, 19)) | G3(M=(3,), A=(7, 12))</t>
@@ -15904,6 +15926,17 @@
       <c r="X6" t="n">
         <v>4577.3795</v>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(1,), A=(1,))</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.628543615341187</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>626.9705</v>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 12, 13, 16, 17, 18, 19), A=(3, 7, 9, 14, 17)) | G1(M=(4,), A=(1, 2, 6, 8, 12, 15)) | G2(M=(11,), A=(11, 13, 16)) | G3(M=(14,), A=(0, 4)) | G4(M=(15,), A=(5, 10, 18, 19))</t>
@@ -15915,6 +15948,17 @@
       <c r="AG6" t="n">
         <v>4830.9039</v>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(1,), A=(1,))</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.628543615341187</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>648.7528</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -15938,6 +15982,17 @@
       <c r="F7" t="n">
         <v>10712.4092</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>(M=(), A=(7,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A*=(0, 1, 2, 3, 4, 5, 6, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02621042728424072</v>
+      </c>
+      <c r="L7" t="n">
+        <v>125.9088</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(2,))</t>
@@ -15949,6 +16004,17 @@
       <c r="O7" t="n">
         <v>2248.6645</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>0.09464401006698608</v>
+      </c>
+      <c r="U7" t="n">
+        <v>295.2616</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 5, 6, 8, 11, 12, 13, 14, 15, 18)) | G1(M=(8,), A=(4, 10, 16)) | G2(M=(), A=(1, 2, 7, 17, 19)) | G3(M=(), A=(3, 9))</t>
@@ -15960,6 +16026,17 @@
       <c r="X7" t="n">
         <v>2490.2566</v>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.09464401006698608</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>214.0744</v>
+      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18), A=(4, 7, 10, 11, 12, 14, 15, 18)) | G1(M=(1, 13), A=(1, 2)) | G2(M=(), A=(0, 3, 6, 13, 19)) | G3(M=(), A=(5, 16)) | G4(M=(), A=(8, 9, 17))</t>
@@ -15971,6 +16048,17 @@
       <c r="AG7" t="n">
         <v>2071.1696</v>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.09464401006698608</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>370.6267</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -15994,6 +16082,17 @@
       <c r="F8" t="n">
         <v>11263.8356</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18, 19)) | (M*=(), A*=(13,))</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01969096064567566</v>
+      </c>
+      <c r="L8" t="n">
+        <v>121.0549</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 1, 2, 3, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(4,))</t>
@@ -16005,6 +16104,17 @@
       <c r="O8" t="n">
         <v>1927.6924</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0.054362952709198</v>
+      </c>
+      <c r="U8" t="n">
+        <v>214.4193</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 12, 13, 14, 15, 16, 17, 18), A=(0, 5, 10, 11, 12, 14, 15, 18, 19)) | G1(M=(11,), A=(4, 6, 8, 9, 17)) | G2(M=(19,), A=(2, 3, 13, 16)) | G3(M=(), A=(1, 7))</t>
@@ -16016,6 +16126,17 @@
       <c r="X8" t="n">
         <v>1932.5665</v>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.054362952709198</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>204.8874</v>
+      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>G0(M=(1, 2, 3, 4, 5, 7, 8, 9, 10, 11, 12, 13, 14, 17, 18), A=(0, 2, 3, 5, 6, 8, 12, 14, 15, 19)) | G1(M=(6, 19), A=()) | G2(M=(15,), A=(9, 16, 17)) | G3(M=(16,), A=(10, 18)) | G4(M=(), A=(1, 4, 7, 11, 13))</t>
@@ -16027,6 +16148,17 @@
       <c r="AG8" t="n">
         <v>1846.0314</v>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>G0(M=(), A=(0,)) | G1(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.054362952709198</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>290.1756</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -16050,6 +16182,17 @@
       <c r="F9" t="n">
         <v>4611.5984</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>(M=(), A=(16,)) | (M*=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.009021669626235962</v>
+      </c>
+      <c r="L9" t="n">
+        <v>59.8915</v>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19)) | G1(M=(), A=(3,)) | G2(M=(), A=(16,))</t>
@@ -16061,6 +16204,17 @@
       <c r="O9" t="n">
         <v>1058.6594</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1299381256103516</v>
+      </c>
+      <c r="U9" t="n">
+        <v>118.7144</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(9,)) | G2(M=(), A=(13,))</t>
@@ -16072,6 +16226,17 @@
       <c r="X9" t="n">
         <v>941.9734</v>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1299381256103516</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>128.3759</v>
+      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>G0(M=(1,), A=(0, 5)) | G1(M=(2, 3, 4, 5, 6, 8, 9, 10, 13, 14, 15, 16, 17, 18), A=(2, 7, 11, 12, 14, 17, 19)) | G2(M=(7, 11, 12), A=(3, 8, 9, 15)) | G3(M=(), A=(1, 6, 10, 16, 18)) | G4(M=(), A=(4, 13))</t>
@@ -16083,6 +16248,17 @@
       <c r="AG9" t="n">
         <v>688.456</v>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(19,))</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1299381256103516</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>134.9008</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -16119,14 +16295,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | (M*=(), A*=(2,))</t>
+          <t>(M=(), A=(12,)) | (M*=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13, 14, 15, 16, 17, 18, 19))</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.02491310238838196</v>
+        <v>0.004291057586669922</v>
       </c>
       <c r="L10" t="n">
-        <v>9.9412</v>
+        <v>4.9774</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -16152,14 +16328,14 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(8,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0.04432523250579834</v>
+        <v>0.02491310238838196</v>
       </c>
       <c r="U10" t="n">
-        <v>9.6966</v>
+        <v>9.6698</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -16185,14 +16361,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 15, 16, 17, 18, 19)) | G1(M=(), A=(14,))</t>
+          <t>G0(M=(0, 1, 3, 4, 6, 7, 9, 10, 12, 13, 15, 16, 18, 19), A=(0, 1, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(2,))</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>0.02767929434776306</v>
+        <v>0.02491310238838196</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.359299999999999</v>
+        <v>16.1294</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -16225,7 +16401,7 @@
         <v>0.02491310238838196</v>
       </c>
       <c r="AM10" t="n">
-        <v>9.5962</v>
+        <v>15.3317</v>
       </c>
     </row>
     <row r="11">
@@ -16261,6 +16437,17 @@
       <c r="I11" t="n">
         <v>649.9398</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>(M=(), A=(12,)) | (M*=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13, 14, 15, 16, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0008695721626281738</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.9252</v>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(9,))</t>
@@ -16283,6 +16470,17 @@
       <c r="R11" t="n">
         <v>1359.6927</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(9,))</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0.001044988632202148</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7.4162</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(1, 4, 6, 10, 14, 15, 18)) | G1(M=(), A=(0, 3, 17)) | G2(M=(), A=(2, 16, 19)) | G3(M=(), A=(5, 7, 8, 9, 11, 12, 13))</t>
@@ -16305,6 +16503,17 @@
       <c r="AA11" t="n">
         <v>1367.2517</v>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(9,))</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.001044988632202148</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>9.7385</v>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(0, 3, 4, 7, 11, 15, 16, 19)) | G1(M=(), A=(1, 8)) | G2(M=(), A=(2, 5, 6, 9, 14, 17, 18)) | G3(M=(), A=(10, 13)) | G4(M=(), A=(12,))</t>
@@ -16327,6 +16536,17 @@
       <c r="AJ11" t="n">
         <v>1503.1489</v>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 4, 6, 8, 10, 12, 14, 16, 18), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19)) | G1(M=(), A=(9,))</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.001044988632202148</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>13.5783</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -16361,6 +16581,17 @@
       <c r="I12" t="n">
         <v>594.7186</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>(M=(), A=(16,)) | (M*=(1, 3, 5, 7, 9, 11, 13, 15, 17, 19), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19))</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.000276029109954834</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.0719</v>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>G0(M=(1, 3, 5, 7, 9, 11, 13, 17, 19), A=(1, 3, 13, 14, 17, 18)) | G1(M=(15,), A=(8, 9, 11, 19)) | G2(M=(), A=(0, 2, 4, 5, 6, 7, 10, 12, 15, 16))</t>
@@ -16383,6 +16614,17 @@
       <c r="R12" t="n">
         <v>1299.4963</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13, 15, 17, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19)) | G1(M=(), A=(16,))</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>0.000276029109954834</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8.3757</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>G0(M=(1, 3, 5, 7, 9, 11, 13, 15, 17, 19), A=(1, 3, 5, 6, 7, 13)) | G1(M=(), A=(0, 2, 4, 9, 10, 14, 17)) | G2(M=(), A=(8, 11, 15, 16)) | G3(M=(), A=(12, 18, 19))</t>
@@ -16405,6 +16647,17 @@
       <c r="AA12" t="n">
         <v>1320.4834</v>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13, 15, 17, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19)) | G1(M=(), A=(16,))</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.000276029109954834</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11.0529</v>
+      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>G0(M=(1, 5, 7, 9, 11, 13), A=(10, 14, 15)) | G1(M=(3,), A=(5, 7, 9, 12, 13, 17)) | G2(M=(15, 17), A=(1, 2, 3, 4, 8, 16, 18)) | G3(M=(19,), A=(0, 11)) | G4(M=(), A=(6, 19))</t>
@@ -16427,6 +16680,17 @@
       <c r="AJ12" t="n">
         <v>1335.2415</v>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>G0(M=(1, 3, 5, 7, 9, 11, 13, 15, 17, 19), A=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19)) | G1(M=(), A=(16,))</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.000276029109954834</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>15.2666</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -16450,6 +16714,17 @@
       <c r="F13" t="n">
         <v>29618.2672</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>(M=(), A=(17,)) | (M*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A*=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 18))</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.02363294363021851</v>
+      </c>
+      <c r="L13" t="n">
+        <v>209.3583</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(), A=(0,))</t>
@@ -16461,6 +16736,17 @@
       <c r="O13" t="n">
         <v>5267.9233</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(1,), A=(1,))</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>2.58705997467041</v>
+      </c>
+      <c r="U13" t="n">
+        <v>435.781</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>G0(M=(0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 14, 15, 16, 17, 18, 19), A=(1, 5, 6, 9, 11, 12, 13, 14, 18)) | G1(M=(13,), A=(0, 3)) | G2(M=(), A=(2, 4, 7, 10, 15, 16, 17)) | G3(M=(), A=(8,))</t>
@@ -16471,6 +16757,17 @@
       </c>
       <c r="X13" t="n">
         <v>4887.3308</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>G0(M=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19), A=(0, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18)) | G1(M=(1,), A=(1,))</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.58705997467041</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>666.7269</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -19745,12 +20042,12 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="M3:U3"/>
     <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="V3:AD3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="AB4:AD4"/>
     <mergeCell ref="P4:R4"/>
@@ -23120,12 +23417,12 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="M3:U3"/>
     <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="V3:AD3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="AB4:AD4"/>
     <mergeCell ref="P4:R4"/>
@@ -24675,12 +24972,12 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="M3:U3"/>
     <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="V3:AD3"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="V3:AD3"/>
+    <mergeCell ref="AE4:AG4"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="AB4:AD4"/>
     <mergeCell ref="P4:R4"/>
